--- a/output/tables/universal_sm_hybrid/hybrid_headline.xlsx
+++ b/output/tables/universal_sm_hybrid/hybrid_headline.xlsx
@@ -477,37 +477,37 @@
         <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>44.47</v>
+        <v>49.78</v>
       </c>
       <c r="D2" t="n">
-        <v>26.23</v>
+        <v>30.83</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5898</v>
+        <v>0.6193</v>
       </c>
       <c r="F2" t="n">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="G2" t="n">
-        <v>14146</v>
+        <v>16303</v>
       </c>
       <c r="H2" t="n">
-        <v>14.15</v>
+        <v>16.3</v>
       </c>
       <c r="I2" t="n">
-        <v>44.47</v>
+        <v>49.78</v>
       </c>
       <c r="J2" t="n">
-        <v>4447</v>
+        <v>4978</v>
       </c>
       <c r="K2" t="n">
-        <v>4.45</v>
+        <v>4.98</v>
       </c>
       <c r="L2" t="n">
-        <v>18593</v>
+        <v>21281</v>
       </c>
       <c r="M2" t="n">
-        <v>18.59</v>
+        <v>21.28</v>
       </c>
     </row>
     <row r="3">
@@ -518,37 +518,37 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>15.22</v>
+        <v>17.56</v>
       </c>
       <c r="D3" t="n">
-        <v>8.98</v>
+        <v>10.88</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5897</v>
+        <v>0.6193</v>
       </c>
       <c r="F3" t="n">
-        <v>524</v>
+        <v>496</v>
       </c>
       <c r="G3" t="n">
-        <v>4706</v>
+        <v>5393</v>
       </c>
       <c r="H3" t="n">
-        <v>4.71</v>
+        <v>5.39</v>
       </c>
       <c r="I3" t="n">
-        <v>15.22</v>
+        <v>17.56</v>
       </c>
       <c r="J3" t="n">
-        <v>1522</v>
+        <v>1756</v>
       </c>
       <c r="K3" t="n">
-        <v>1.52</v>
+        <v>1.76</v>
       </c>
       <c r="L3" t="n">
-        <v>6228</v>
+        <v>7150</v>
       </c>
       <c r="M3" t="n">
-        <v>6.23</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="4">
@@ -559,37 +559,37 @@
         <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>29.25</v>
+        <v>32.22</v>
       </c>
       <c r="D4" t="n">
-        <v>17.25</v>
+        <v>19.95</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5897</v>
+        <v>0.6193</v>
       </c>
       <c r="F4" t="n">
         <v>547</v>
       </c>
       <c r="G4" t="n">
-        <v>9440</v>
+        <v>10910</v>
       </c>
       <c r="H4" t="n">
-        <v>9.44</v>
+        <v>10.91</v>
       </c>
       <c r="I4" t="n">
-        <v>29.25</v>
+        <v>32.22</v>
       </c>
       <c r="J4" t="n">
-        <v>2925</v>
+        <v>3222</v>
       </c>
       <c r="K4" t="n">
-        <v>2.92</v>
+        <v>3.22</v>
       </c>
       <c r="L4" t="n">
-        <v>12365</v>
+        <v>14132</v>
       </c>
       <c r="M4" t="n">
-        <v>12.37</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="5">
@@ -600,37 +600,37 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>44.47</v>
+        <v>49.78</v>
       </c>
       <c r="D5" t="n">
-        <v>35.58</v>
+        <v>39.83</v>
       </c>
       <c r="E5" t="n">
         <v>0.8</v>
       </c>
       <c r="F5" t="n">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="G5" t="n">
-        <v>19092</v>
+        <v>21093</v>
       </c>
       <c r="H5" t="n">
-        <v>19.09</v>
+        <v>21.09</v>
       </c>
       <c r="I5" t="n">
-        <v>44.47</v>
+        <v>49.78</v>
       </c>
       <c r="J5" t="n">
-        <v>4447</v>
+        <v>4978</v>
       </c>
       <c r="K5" t="n">
-        <v>4.45</v>
+        <v>4.98</v>
       </c>
       <c r="L5" t="n">
-        <v>23540</v>
+        <v>26071</v>
       </c>
       <c r="M5" t="n">
-        <v>23.54</v>
+        <v>26.07</v>
       </c>
     </row>
     <row r="6">
@@ -641,37 +641,37 @@
         <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>44.47</v>
+        <v>49.78</v>
       </c>
       <c r="D6" t="n">
-        <v>44.47</v>
+        <v>49.78</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="G6" t="n">
-        <v>23866</v>
+        <v>26366</v>
       </c>
       <c r="H6" t="n">
-        <v>23.87</v>
+        <v>26.37</v>
       </c>
       <c r="I6" t="n">
-        <v>44.47</v>
+        <v>49.78</v>
       </c>
       <c r="J6" t="n">
-        <v>4447</v>
+        <v>4978</v>
       </c>
       <c r="K6" t="n">
-        <v>4.45</v>
+        <v>4.98</v>
       </c>
       <c r="L6" t="n">
-        <v>28313</v>
+        <v>31345</v>
       </c>
       <c r="M6" t="n">
-        <v>28.31</v>
+        <v>31.34</v>
       </c>
     </row>
   </sheetData>
@@ -713,22 +713,22 @@
         <v>25</v>
       </c>
       <c r="B2" t="n">
-        <v>4447</v>
+        <v>4978</v>
       </c>
       <c r="C2" t="n">
-        <v>4.45</v>
+        <v>4.98</v>
       </c>
       <c r="D2" t="n">
-        <v>44.47</v>
+        <v>49.78</v>
       </c>
       <c r="E2" t="n">
-        <v>44.47</v>
+        <v>49.78</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7898</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="3">
@@ -736,13 +736,13 @@
         <v>26</v>
       </c>
       <c r="B3" t="n">
-        <v>1709</v>
+        <v>1882</v>
       </c>
       <c r="C3" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="D3" t="n">
-        <v>44.47</v>
+        <v>49.78</v>
       </c>
       <c r="E3" t="n">
         <v>0.03</v>
@@ -751,7 +751,7 @@
         <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9089</v>
+        <v>0.8829</v>
       </c>
     </row>
     <row r="4">
@@ -759,22 +759,22 @@
         <v>27</v>
       </c>
       <c r="B4" t="n">
-        <v>3643</v>
+        <v>4025</v>
       </c>
       <c r="C4" t="n">
-        <v>3.64</v>
+        <v>4.03</v>
       </c>
       <c r="D4" t="n">
-        <v>44.47</v>
+        <v>49.78</v>
       </c>
       <c r="E4" t="n">
-        <v>28.06</v>
+        <v>30.99</v>
       </c>
       <c r="F4" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8451</v>
+        <v>0.8082</v>
       </c>
     </row>
     <row r="5">
@@ -782,22 +782,22 @@
         <v>28</v>
       </c>
       <c r="B5" t="n">
-        <v>5270</v>
+        <v>5836</v>
       </c>
       <c r="C5" t="n">
-        <v>5.27</v>
+        <v>5.84</v>
       </c>
       <c r="D5" t="n">
-        <v>60.31</v>
+        <v>66.91</v>
       </c>
       <c r="E5" t="n">
-        <v>44.47</v>
+        <v>49.78</v>
       </c>
       <c r="F5" t="n">
         <v>87</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7416</v>
+        <v>0.7047</v>
       </c>
     </row>
   </sheetData>
